--- a/www/flightdata/xlsx/eoss-356.xlsx
+++ b/www/flightdata/xlsx/eoss-356.xlsx
@@ -3105,7 +3105,7 @@
         <v>27576.17</v>
       </c>
       <c r="I2">
-        <v>599</v>
+        <v>381</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
